--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U41"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +623,8 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,6 +704,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -771,6 +785,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -850,6 +866,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -929,6 +947,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1008,6 +1028,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1087,6 +1109,8 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1166,6 +1190,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1245,6 +1271,8 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1324,6 +1352,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1403,6 +1433,8 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1482,6 +1514,8 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1561,6 +1595,8 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1640,6 +1676,8 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1757,8 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1798,6 +1838,8 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1877,6 +1919,8 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1956,6 +2000,8 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2035,6 +2081,8 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2114,6 +2162,8 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2193,6 +2243,8 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2272,6 +2324,8 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2351,6 +2405,8 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2430,6 +2486,8 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2509,6 +2567,8 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2588,6 +2648,8 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2667,6 +2729,8 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2746,6 +2810,8 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2825,6 +2891,8 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2904,6 +2972,8 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2983,6 +3053,8 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3062,6 +3134,8 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3071,37 +3145,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cagliari x Inter</t>
+          <t>Deportivo Moron x San Miguel</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Deportivo Moron</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3110,37 +3184,47 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="K34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>11.63</v>
+        <v>9.52</v>
       </c>
       <c r="M34" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>9.19</v>
+      </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="W34" t="n">
+        <v>9.19</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3150,37 +3234,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BOSNIA 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina x Borac Banja Luka</t>
+          <t>Cagliari x Inter</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3189,20 +3273,20 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="K35" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="L35" t="n">
-        <v>18.52</v>
+        <v>11.63</v>
       </c>
       <c r="M35" t="n">
         <v>100</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3220,6 +3304,8 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3234,22 +3320,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>BOSNIA 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Flamengo x Botafogo FR</t>
+          <t>Radnik Bijeljina x Borac Banja Luka</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3268,20 +3354,20 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="K36" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="L36" t="n">
-        <v>20.83</v>
+        <v>18.52</v>
       </c>
       <c r="M36" t="n">
         <v>100</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3299,6 +3385,8 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3313,22 +3401,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>America MG x Ponte Preta</t>
+          <t>Flamengo x Botafogo FR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3347,20 +3435,20 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="K37" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="L37" t="n">
-        <v>12.2</v>
+        <v>20.83</v>
       </c>
       <c r="M37" t="n">
         <v>100</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3378,6 +3466,8 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3387,37 +3477,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sport Boys (Per) x Sporting Cristal</t>
+          <t>America MG x Ponte Preta</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sport Boys (Per)</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3426,20 +3516,20 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="L38" t="n">
-        <v>6.25</v>
+        <v>12.2</v>
       </c>
       <c r="M38" t="n">
         <v>100</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3457,6 +3547,8 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3466,37 +3558,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Carabobo FC x Zamora FC</t>
+          <t>Corinthians x Santos</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3505,20 +3597,20 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>5.6</v>
+        <v>22</v>
       </c>
       <c r="K39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>21.74</v>
+        <v>9.52</v>
       </c>
       <c r="M39" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3533,9 +3625,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>9.19</v>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3545,37 +3645,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MEXICO 1</t>
+          <t>PERU 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Toluca x FC Juarez</t>
+          <t>Sport Boys (Per) x Sporting Cristal</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Sport Boys (Per)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3584,20 +3684,20 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>17.86</v>
+        <v>6.25</v>
       </c>
       <c r="M40" t="n">
         <v>100</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3615,6 +3715,8 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3634,19 +3736,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Carabobo x Zamora</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+          <t>Carabobo FC x Zamora FC</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Carabobo FC</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Zamora FC</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3655,13 +3765,13 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="K41" t="n">
         <v>1.4</v>
       </c>
       <c r="L41" t="n">
-        <v>9.09</v>
+        <v>21.74</v>
       </c>
       <c r="M41" t="n">
         <v>100</v>
@@ -3673,25 +3783,268 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VENEZUELA 1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Carabobo x Zamora</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Match Odds (Away)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>12</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L42" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="M42" t="n">
+        <v>100</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="P41" t="n">
+      <c r="P42" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="n">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
         <v>8.77</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T42" t="n">
         <v>1</v>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>LIQUIDADO</t>
         </is>
       </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ECUADOR 1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Emelec x CD Leones del Norte</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CD Leones del Norte</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>21</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>10</v>
+      </c>
+      <c r="M43" t="n">
+        <v>200</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S43" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MEXICO 1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Toluca x FC Juarez</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L44" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="M44" t="n">
+        <v>100</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4x0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1x6</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1x6</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2x5</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4x2</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0x4</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>5x2</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2306,12 +2306,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2387,12 +2387,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4x1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2468,12 +2468,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2711,12 +2711,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -3035,12 +3035,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3286,12 +3286,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3529,12 +3529,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -3778,12 +3778,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>1x6</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>1x6</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>2x5</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4x2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>0x4</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5x2</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2306,12 +2306,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2387,12 +2387,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>4x1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2468,12 +2468,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2711,12 +2711,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -3035,12 +3035,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3286,12 +3286,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3529,12 +3529,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -3778,12 +3778,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-30.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3610,19 +3610,19 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🔴 RED</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -3938,19 +3938,19 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S43" t="n">
